--- a/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honoré est à la basse-cour. Maman tient sa main. Un coq chante. Une poule picore. Un poussin suit. Maman dit : coq, poule, poussin. Ce sont trois noms. Trois noms de la famille. Honoré répète. Coq. Poule. Poussin. Papa montre le chien. Chien, chienne, chiot. Encore trois noms de la famille. Honoré sourit. Il dit : chiot. Le chiot est petit. Ça sent la paille.</t>
+          <t>Honoré est à la basse-cour. Maman tient sa main. Un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Ce sont trois noms. Trois noms de la famille. Honoré répète. Coq. Poule. Poussin. Papa montre le chien. Chien, chienne, chiot. Encore trois noms de la famille. Honoré sourit. Chiot. Le chiot est petit. Ça sent la paille.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré est à la basse-cour. Maman tient sa main. Un coq chante. Une poule picore. Un poussin suit.
+maman|Coq, poule, poussin. Ce sont trois noms. Trois noms de la famille.
+narrateur|Honoré répète. Coq. Poule. Poussin. Papa montre le chien. Chien, chienne, chiot. Encore trois noms de la famille. Honoré sourit.
+narrateur|Chiot.
+narrateur|Le chiot est petit. Ça sent la paille.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré a dit les trois noms. Coq, poule, poussin. Chien, chienne, chiot.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Honoré sent la paille. Maman sourit. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Le chiot est petit. Ça sent la paille.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,11 @@
           <t>narrateur|Honoré a dit les trois noms. Coq, poule, poussin. Chien, chienne, chiot.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1847,7 @@
           <t>narrateur|Honoré sent la paille. Maman sourit. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Honoré dit les trois noms</t>
+          <t>Le poulain blanc</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mila veut que le poulain blanc vienne près de la barrière. Ils restent avec papa et maman. Le poulain s'approche. Elle dit les trois noms.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honoré est à la basse-cour. Maman tient sa main. Un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Ce sont trois noms. Trois noms de la famille. Honoré répète. Coq. Poule. Poussin. Papa montre le chien. Chien, chienne, chiot. Encore trois noms de la famille. Honoré sourit. Chiot. Le chiot est petit. Ça sent la paille.</t>
+          <t>La brume repose sur le pré. L'herbe brille, toute mouillée. Ça sent le foin humide. Une goutte tombe du bois. La barrière est froide. Tes boutons, Mila. Maman noue le manteau. On va voir les bêtes ? Le blanc. Je veux le blanc. On marche ensemble. Le chemin est gras. Les bottes font un petit bruit. Floc, floc. Tu tiens ma main ? Oui, maman. Un oiseau part du buisson. Le pré s'ouvre, tout large. En ce moment, Mila tient la barrière. Le bois est rêche sous ses doigts. Trois bêtes mangent l'herbe. Tu les vois ? Oui. Un cheval brun lève la tête. Sa crinière est sombre. Une jument grise broute près de lui. Son ventre est rond, tout calme. Derrière, un poulain blanc. Il est petit. Il a une étoile au front. Le blanc ! Il vient ? On reste ici. Près de la barrière. Avec nous. Mila pose un pied vers l'herbe. L'herbe du pré, de l'autre côté. Les pieds restent ici, Mila. On regarde. Il est loin. On attend. Tout doux. Le poulain se cache un peu. La jument passe devant. On ne voit plus l'étoile. Il est parti ? Non. Il est là. Cheval. Jument. Poulain. Trois noms de la famille. Cheval. Jument. Poulain. Le petit, c'est le poulain. Mila répète, tout bas. Poulain. Un souffle blanc sort du pré. Le poulain avance d'un pas. Puis d'un autre. Tu vois l'étoile ? Oui, papa. Le bois de la barrière tremble un peu. Mila serre le bois. Elle ne tend pas la main. On reste près de nous. Je reste.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honoré est à la basse-cour. Maman tient sa main. Un coq chante. Une poule picore. Un poussin suit. Maman dit : coq, poule, poussin. Ce sont &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Trois noms de la famille. Honoré répète. Coq. Poule. Poussin. Papa montre le chien. Chien, chienne, chiot. Encore trois noms de la famille. Honoré sourit. Il dit : chiot. Le chiot est petit. Ça sent la paille.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La brume repose sur le pré. L'herbe brille, toute mouillée. Ça sent le foin humide. Une goutte tombe du bois. La barrière est froide. Tes boutons, Mila. Maman noue le manteau. On va voir les bêtes ? Le blanc. Je veux le blanc. On marche ensemble. Le chemin est gras. Les bottes font un petit bruit. Floc, floc. Tu tiens ma main ? Oui, maman. Un oiseau part du buisson. Le pré s'ouvre, tout large. En ce moment, Mila tient la barrière. Le bois est rêche sous ses doigts. Trois bêtes mangent l'herbe. Tu les vois ? Oui. Un cheval brun lève la tête. Sa crinière est sombre. Une jument grise broute près de lui. Son ventre est rond, tout calme. Derrière, un poulain blanc. Il est petit. Il a une étoile au front. Le blanc ! Il vient ? On reste ici. Près de la barrière. Avec nous. Mila pose un pied vers l'herbe. L'herbe du pré, de l'autre côté. Les pieds restent ici, Mila. On regarde. Il est loin. On attend. Tout doux. Le poulain se cache un peu. La jument passe devant. On ne voit plus l'étoile. Il est parti ? Non. Il est là. Cheval. Jument. Poulain. Trois noms de la famille. Cheval. Jument. Poulain. Le petit, c'est le poulain. Mila répète, tout bas. Poulain. Un souffle blanc sort du pré. Le poulain avance d'un pas. Puis d'un autre. Tu vois l'étoile ? Oui, papa. Le bois de la barrière tremble un peu. Mila serre le bois. Elle ne tend pas la main. On reste près de nous. Je reste.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Honoré est à la basse-cour. Maman tient sa main. Un coq chante. Une poule picore. Un poussin suit.
-maman|Coq, poule, poussin. Ce sont trois noms. Trois noms de la famille.
-narrateur|Honoré répète. Coq. Poule. Poussin. Papa montre le chien. Chien, chienne, chiot. Encore trois noms de la famille. Honoré sourit.
-narrateur|Chiot.
-narrateur|Le chiot est petit. Ça sent la paille.</t>
+          <t>narrateur|La brume repose sur le pré.
+narrateur|L'herbe brille, toute mouillée.
+narrateur|Ça sent le foin humide.
+narrateur|Une goutte tombe du bois.
+narrateur|La barrière est froide.
+maman|Tes boutons, Mila.
+narrateur|Maman noue le manteau.
+papa|On va voir les bêtes ?
+enfant-f|Le blanc.
+enfant-f|Je veux le blanc.
+papa|On marche ensemble.
+narrateur|Le chemin est gras.
+narrateur|Les bottes font un petit bruit.
+narrateur|Floc, floc.
+maman|Tu tiens ma main ?
+enfant-f|Oui, maman.
+narrateur|Un oiseau part du buisson.
+narrateur|Le pré s'ouvre, tout large.
+narrateur|En ce moment, Mila tient la barrière.
+narrateur|Le bois est rêche sous ses doigts.
+narrateur|Trois bêtes mangent l'herbe.
+papa|Tu les vois ?
+enfant-f|Oui.
+narrateur|Un cheval brun lève la tête.
+narrateur|Sa crinière est sombre.
+narrateur|Une jument grise broute près de lui.
+narrateur|Son ventre est rond, tout calme.
+narrateur|Derrière, un poulain blanc.
+narrateur|Il est petit.
+narrateur|Il a une étoile au front.
+enfant-f|Le blanc !
+enfant-f|Il vient ?
+maman|On reste ici.
+maman|Près de la barrière.
+papa|Avec nous.
+narrateur|Mila pose un pied vers l'herbe.
+narrateur|L'herbe du pré, de l'autre côté.
+maman|Les pieds restent ici, Mila.
+maman|On regarde.
+enfant-f|Il est loin.
+papa|On attend.
+papa|Tout doux.
+narrateur|Le poulain se cache un peu.
+narrateur|La jument passe devant.
+narrateur|On ne voit plus l'étoile.
+enfant-f|Il est parti ?
+maman|Non.
+maman|Il est là.
+papa|Cheval.
+papa|Jument.
+papa|Poulain.
+maman|Trois noms de la famille.
+enfant-f|Cheval.
+enfant-f|Jument.
+enfant-f|Poulain.
+maman|Le petit, c'est le poulain.
+narrateur|Mila répète, tout bas.
+enfant-f|Poulain.
+narrateur|Un souffle blanc sort du pré.
+narrateur|Le poulain avance d'un pas.
+narrateur|Puis d'un autre.
+papa|Tu vois l'étoile ?
+enfant-f|Oui, papa.
+narrateur|Le bois de la barrière tremble un peu.
+narrateur|Mila serre le bois.
+narrateur|Elle ne tend pas la main.
+maman|On reste près de nous.
+enfant-f|Je reste.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1423,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
+          <t>Quel est le petit de la jument ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le coq, la poule, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Quel est le petit de la jument ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1438,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>poussin</t>
+          <t>poulain</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>poussin | le poussin | petit | le petit</t>
+          <t>poulain | le poulain | petit | le petit</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1458,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le petit du coq et de la poule. Qui est-ce ?</t>
+          <t>Le petit du cheval et de la jument. Qui est-ce ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1507,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1579,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Quel est le petit de la jument ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1606,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Honoré a dit les trois noms. Coq, poule, poussin. Chien, chienne, chiot.</t>
+          <t>Le poulain blanc s'approche encore. Ses sabots tapent l'herbe mouillée. Toc, tout mou. Le petit, c'est le poulain. Poulain. Bravo. Tu as dit les trois noms. Le cheval brun écoute. La jument grise broute. Le poulain lève le nez. Sa moustache est mouillée. Il a une étoile. Oui. Comme un dessin. Tu restes à la barrière ? Oui, maman. Mila a les mains sur le bois. Le bois sent la pluie d'hier. Le poulain vient tout près. On entend son souffle. Il est venu. Pour moi. Pour regarder. On est doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honoré a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Coq, poule, poussin. Chien, chienne, chiot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le poulain blanc s'approche encore. Ses sabots tapent l'herbe mouillée. Toc, tout mou. Le petit, c'est le poulain. Poulain. Bravo. Tu as dit les trois noms. Le cheval brun écoute. La jument grise broute. Le poulain lève le nez. Sa moustache est mouillée. Il a une étoile. Oui. Comme un dessin. Tu restes à la barrière ? Oui, maman. Mila a les mains sur le bois. Le bois sent la pluie d'hier. Le poulain vient tout près. On entend son souffle. Il est venu. Pour moi. Pour regarder. On est doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1593,14 +1667,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,7 +1750,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Honoré a dit les trois noms. Coq, poule, poussin. Chien, chienne, chiot.</t>
+          <t>narrateur|Le poulain blanc s'approche encore.
+narrateur|Ses sabots tapent l'herbe mouillée.
+narrateur|Toc, tout mou.
+papa|Le petit, c'est le poulain.
+enfant-f|Poulain.
+maman|Bravo.
+maman|Tu as dit les trois noms.
+narrateur|Le cheval brun écoute.
+narrateur|La jument grise broute.
+narrateur|Le poulain lève le nez.
+narrateur|Sa moustache est mouillée.
+enfant-f|Il a une étoile.
+papa|Oui.
+papa|Comme un dessin.
+maman|Tu restes à la barrière ?
+enfant-f|Oui, maman.
+narrateur|Mila a les mains sur le bois.
+narrateur|Le bois sent la pluie d'hier.
+narrateur|Le poulain vient tout près.
+narrateur|On entend son souffle.
+papa|Il est venu.
+enfant-f|Pour moi.
+maman|Pour regarder.
+maman|On est doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1708,12 +1805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Honoré sent la paille. Maman sourit. Ils rentrent.</t>
+          <t>Le poulain blanc boit la rosée. Sa langue prend une goutte. Il boit. Oui. Comme nous, le matin. Cheval, jument, poulain. Trois noms. Mila chuchote encore. Poulain. L'étoile au front brille un peu. La brume s'en va. On rentre ? Encore un peu. Un peu, oui. Ils restent contre le bois. Le pré sent l'herbe coupée. Le poulain secoue l'oreille. Merci, Mila. Tu as regardé sans bouger.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Honoré sent la paille. Maman sourit. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le poulain blanc boit la rosée. Sa langue prend une goutte. Il boit. Oui. Comme nous, le matin. Cheval, jument, poulain. Trois noms. Mila chuchote encore. Poulain. L'étoile au front brille un peu. La brume s'en va. On rentre ? Encore un peu. Un peu, oui. Ils restent contre le bois. Le pré sent l'herbe coupée. Le poulain secoue l'oreille. Merci, Mila. Tu as regardé sans bouger.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,14 +1866,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1941,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Honoré sent la paille. Maman sourit. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le poulain blanc boit la rosée.
+narrateur|Sa langue prend une goutte.
+enfant-f|Il boit.
+papa|Oui.
+papa|Comme nous, le matin.
+maman|Cheval, jument, poulain.
+enfant-f|Trois noms.
+narrateur|Mila chuchote encore.
+enfant-f|Poulain.
+narrateur|L'étoile au front brille un peu.
+narrateur|La brume s'en va.
+papa|On rentre ?
+enfant-f|Encore un peu.
+maman|Un peu, oui.
+narrateur|Ils restent contre le bois.
+narrateur|Le pré sent l'herbe coupée.
+narrateur|Le poulain secoue l'oreille.
+maman|Merci, Mila.
+maman|Tu as regardé sans bouger.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,12 +1986,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le blanc est venu. Le poulain, oui. Une goutte glisse sur la barrière. Elle tombe dans l'herbe. Le pré redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le blanc est venu. Le poulain, oui. Une goutte glisse sur la barrière. Elle tombe dans l'herbe. Le pré redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,14 +2047,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2012,10 +2126,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-f|Le blanc est venu.
+papa|Le poulain, oui.
+narrateur|Une goutte glisse sur la barrière.
+narrateur|Elle tombe dans l'herbe.
+narrateur|Le pré redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2189,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-09.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>basse-cour</t>
+          <t>pré derrière la barrière, matin brumeux</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honoré, maman, papa</t>
+          <t>Mila, maman, papa</t>
         </is>
       </c>
     </row>
